--- a/sources/hwoarang_step9.xlsx
+++ b/sources/hwoarang_step9.xlsx
@@ -426,7 +426,7 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col hidden="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col hidden="1" min="10" max="10"/>
@@ -6996,27 +6996,27 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3 ,3 ,d+3 ,4 [F]</t>
+          <t>3 ,3 ,d+3 ,4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7160,27 +7160,27 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3 ,3 ,4 [F]</t>
+          <t>3 ,3 ,4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7324,27 +7324,27 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3 ,3 ,3 &lt;4 [F]</t>
+          <t>3 ,3 ,3 &lt;4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -14997,12 +14997,12 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">

--- a/sources/hwoarang_step9.xlsx
+++ b/sources/hwoarang_step9.xlsx
@@ -10325,6 +10325,11 @@
           <t>Cheap Shot – Retreat</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>14</t>
@@ -10337,7 +10342,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>+12 -16</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10347,7 +10352,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>+23 -5</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -10357,32 +10362,32 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>+23 -5</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>25,-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>h-</t>
+          <t>h</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">

--- a/sources/hwoarang_step9.xlsx
+++ b/sources/hwoarang_step9.xlsx
@@ -1033,6 +1033,11 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
@@ -1100,6 +1105,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
@@ -1167,6 +1177,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
@@ -1232,6 +1247,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>In RFF 2+5 throws don't work.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -15473,6 +15493,11 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
@@ -15523,6 +15548,11 @@
       <c r="T179" t="inlineStr">
         <is>
           <t>mhhLmmlhmh</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
